--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487193_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487193_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.3713</v>
+        <v>9.706200000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>9.212199999999999</v>
+        <v>6.6274</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1591</v>
+        <v>3.0788</v>
       </c>
       <c r="G2" t="n">
         <v>5.5671</v>
@@ -610,13 +610,13 @@
         <v>1.3511</v>
       </c>
       <c r="S2" t="n">
-        <v>5.1709</v>
+        <v>2.5058</v>
       </c>
       <c r="T2" t="n">
-        <v>3.9739</v>
+        <v>1.3891</v>
       </c>
       <c r="U2" t="n">
-        <v>1.197</v>
+        <v>1.1167</v>
       </c>
       <c r="V2" t="n">
         <v>2.2123</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.2073</v>
+        <v>7.7526</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1016</v>
+        <v>3.7807</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1057</v>
+        <v>3.9719</v>
       </c>
       <c r="G3" t="n">
         <v>3.7948</v>
@@ -688,13 +688,13 @@
         <v>1.5441</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6405</v>
+        <v>1.1858</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6848</v>
+        <v>-0.0056</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3252</v>
+        <v>1.1914</v>
       </c>
       <c r="V3" t="n">
         <v>1.228</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.8296</v>
+        <v>7.5643</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7136</v>
+        <v>3.0735</v>
       </c>
       <c r="F4" t="n">
-        <v>4.116</v>
+        <v>4.4908</v>
       </c>
       <c r="G4" t="n">
         <v>5.0629</v>
@@ -766,13 +766,13 @@
         <v>1.5441</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4336</v>
+        <v>0.3011</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7139</v>
+        <v>-0.3539</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2802</v>
+        <v>0.655</v>
       </c>
       <c r="V4" t="n">
         <v>0.6562</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.2629</v>
+        <v>5.8964</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2133</v>
+        <v>1.8737</v>
       </c>
       <c r="F5" t="n">
-        <v>4.0495</v>
+        <v>4.0228</v>
       </c>
       <c r="G5" t="n">
         <v>5.7177</v>
@@ -844,13 +844,13 @@
         <v>2.3161</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5175</v>
+        <v>1.1511</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8487</v>
+        <v>-0.1883</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3662</v>
+        <v>1.3395</v>
       </c>
       <c r="V5" t="n">
         <v>0.5717</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>5.221</v>
+        <v>5.2993</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3293</v>
+        <v>2.6485</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8917</v>
+        <v>2.6507</v>
       </c>
       <c r="G6" t="n">
         <v>3.1831</v>
@@ -922,13 +922,13 @@
         <v>1.5441</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4588</v>
+        <v>1.5371</v>
       </c>
       <c r="T6" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.3907</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3874</v>
+        <v>1.1464</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.7279</v>
+        <v>3.6258</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9540999999999999</v>
+        <v>1.1732</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7738</v>
+        <v>2.4526</v>
       </c>
       <c r="G7" t="n">
         <v>2.8175</v>
@@ -1000,13 +1000,13 @@
         <v>0.386</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5896</v>
+        <v>0.4875</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2829</v>
+        <v>-0.0638</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.5512</v>
       </c>
       <c r="V7" t="n">
         <v>0.8999</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0825</v>
+        <v>1.1083</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2084</v>
+        <v>-0.0488</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2909</v>
+        <v>1.1571</v>
       </c>
       <c r="G8" t="n">
         <v>0.9962</v>
@@ -1078,13 +1078,13 @@
         <v>0.193</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1791</v>
+        <v>0.2049</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3569</v>
+        <v>-0.1973</v>
       </c>
       <c r="U8" t="n">
-        <v>0.536</v>
+        <v>0.4022</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2859</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. BONILLA HERNANDEZ</t>
+          <t>M. KHATIASHVILI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0045</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.185</v>
+        <v>-0.975</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1804</v>
+        <v>1.4775</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2898</v>
+        <v>0.9774</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0049</v>
+        <v>-0.9076</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2849</v>
+        <v>1.885</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4886</v>
+        <v>1.4178</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0569</v>
+        <v>0.1811</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5455</v>
+        <v>1.2367</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8012</v>
+        <v>-0.4403</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0618</v>
+        <v>-1.0886</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2606</v>
+        <v>0.6483</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.579</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3511</v>
+        <v>1.158</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5785</v>
+        <v>1.2622</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9479</v>
+        <v>0.5024</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6306</v>
+        <v>0.7598</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4038</v>
+        <v>0.0771</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0369</v>
+        <v>0.3637</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3669</v>
+        <v>-0.2866</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2048</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.199</v>
+        <v>0.2819</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.119</v>
+        <v>0.2816</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.08</v>
+        <v>0.0003</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. KHATIASHVILI</t>
+          <t>O. IBARROLA ITURRIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6585</v>
+        <v>-0.6438</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8951</v>
+        <v>-3.8915</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2366</v>
+        <v>3.2477</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9774</v>
+        <v>-3.8646</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9076</v>
+        <v>-2.7801</v>
       </c>
       <c r="I11" t="n">
-        <v>1.885</v>
+        <v>-1.0846</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4178</v>
+        <v>-4.0517</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1811</v>
+        <v>-2.1789</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2367</v>
+        <v>-1.8728</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4403</v>
+        <v>0.1871</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0886</v>
+        <v>-0.6012</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6483</v>
+        <v>0.7883</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.7371</v>
+        <v>0.193</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R11" t="n">
-        <v>1.158</v>
+        <v>2.1231</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1011</v>
+        <v>1.514</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4177</v>
+        <v>0.5764</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5188</v>
+        <v>0.9376</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O. IBARROLA ITURRIA</t>
+          <t>E. BONILLA HERNANDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2912</v>
+        <v>-0.652</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.3516</v>
+        <v>-1.886</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0604</v>
+        <v>1.234</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.8646</v>
+        <v>-1.2898</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.7801</v>
+        <v>-1.0049</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.0846</v>
+        <v>-0.2849</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.0517</v>
+        <v>-0.4886</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.1789</v>
+        <v>0.0569</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8728</v>
+        <v>-0.5455</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1871</v>
+        <v>-0.8012</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6012</v>
+        <v>-1.0618</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7883</v>
+        <v>0.2606</v>
       </c>
       <c r="P12" t="n">
-        <v>0.193</v>
+        <v>-0.579</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1231</v>
+        <v>1.3511</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8666</v>
+        <v>0.931</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1164</v>
+        <v>0.2469</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7502</v>
+        <v>0.6841</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5138</v>
+        <v>0.2859</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5138</v>
+        <v>0.2859</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>39.34450000000001</v>
+        <v>40.2367</v>
       </c>
       <c r="E13" t="n">
-        <v>11.8471</v>
+        <v>12.7394</v>
       </c>
       <c r="F13" t="n">
-        <v>27.4972</v>
+        <v>27.4973</v>
       </c>
       <c r="G13" t="n">
         <v>22.7575</v>
@@ -1444,7 +1444,7 @@
         <v>16.782</v>
       </c>
       <c r="K13" t="n">
-        <v>6.446399999999999</v>
+        <v>6.4464</v>
       </c>
       <c r="L13" t="n">
         <v>10.3356</v>
@@ -1453,7 +1453,7 @@
         <v>5.9758</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.609500000000001</v>
+        <v>-4.6095</v>
       </c>
       <c r="O13" t="n">
         <v>10.5851</v>
@@ -1468,13 +1468,13 @@
         <v>13.5107</v>
       </c>
       <c r="S13" t="n">
-        <v>10.47</v>
+        <v>11.3624</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6857</v>
+        <v>2.5782</v>
       </c>
       <c r="U13" t="n">
-        <v>8.784099999999999</v>
+        <v>8.784200000000002</v>
       </c>
       <c r="V13" t="n">
         <v>7.081899999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.5078</v>
+        <v>-0.3739</v>
       </c>
       <c r="E14" t="n">
         <v>-0.2767</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.231</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-0.3997</v>
@@ -1546,13 +1546,13 @@
         <v>0.386</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2082</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="T14" t="n">
         <v>-0.2974</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0892</v>
+        <v>0.2231</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2859</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.772</v>
+        <v>-0.8477</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.4475</v>
+        <v>-1.1471</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6755</v>
+        <v>0.2994</v>
       </c>
       <c r="G15" t="n">
         <v>-0.411</v>
@@ -1624,13 +1624,13 @@
         <v>2.5091</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3067</v>
+        <v>-0.3824</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.9485</v>
+        <v>-1.6481</v>
       </c>
       <c r="U15" t="n">
-        <v>1.6418</v>
+        <v>1.2657</v>
       </c>
       <c r="V15" t="n">
         <v>-1.5983</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. GÓMEZ LÓPEZ</t>
+          <t>G. PEREZ CABRERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.8339</v>
+        <v>-1.5218</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.9068</v>
+        <v>0.2033</v>
       </c>
       <c r="F16" t="n">
-        <v>0.07290000000000001</v>
+        <v>-1.7251</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0116</v>
+        <v>-0.2996</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0641</v>
+        <v>0.2359</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9475</v>
+        <v>-0.5355</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5848</v>
+        <v>1.8556</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0828</v>
+        <v>1.2779</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6676</v>
+        <v>0.5777</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4268</v>
+        <v>-2.1552</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1469</v>
+        <v>-1.042</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2799</v>
+        <v>-1.1132</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.193</v>
+        <v>0.386</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>0.772</v>
+        <v>2.3161</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6293</v>
+        <v>-1.3223</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3569</v>
+        <v>-1.236</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2723</v>
+        <v>-0.0863</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. PEREZ CABRERA</t>
+          <t>E. GÓMEZ LÓPEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.4832</v>
+        <v>-1.6204</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1973</v>
+        <v>-1.9068</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2859</v>
+        <v>0.2864</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2996</v>
+        <v>-1.0116</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2359</v>
+        <v>-0.0641</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5355</v>
+        <v>-0.9475</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8556</v>
+        <v>-0.5848</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2779</v>
+        <v>0.0828</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5777</v>
+        <v>-0.6676</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1552</v>
+        <v>-0.4268</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.042</v>
+        <v>-0.1469</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1132</v>
+        <v>-0.2799</v>
       </c>
       <c r="P17" t="n">
-        <v>0.386</v>
+        <v>-0.193</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3161</v>
+        <v>0.772</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.2837</v>
+        <v>-0.4158</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.6366</v>
+        <v>-0.3569</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6471</v>
+        <v>-0.0588</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.8502</v>
+        <v>-3.1437</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4021</v>
+        <v>0.0015</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.2523</v>
+        <v>-3.1452</v>
       </c>
       <c r="G18" t="n">
         <v>-1.3179</v>
@@ -1858,13 +1858,13 @@
         <v>0.386</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4045</v>
+        <v>-0.698</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3252</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7297</v>
+        <v>-0.6227</v>
       </c>
       <c r="V18" t="n">
         <v>-1.5138</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.7792</v>
+        <v>-3.7524</v>
       </c>
       <c r="E19" t="n">
         <v>-3.5278</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2514</v>
+        <v>-0.2246</v>
       </c>
       <c r="G19" t="n">
         <v>-1.169</v>
@@ -1936,13 +1936,13 @@
         <v>0.965</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6802</v>
+        <v>-0.6534</v>
       </c>
       <c r="T19" t="n">
         <v>-0.8183</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1381</v>
+        <v>0.1649</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. MERKVILADZE</t>
+          <t>M. MENDEZ MADERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.6085</v>
+        <v>-4.7888</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.1615</v>
+        <v>-3.8138</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.447</v>
+        <v>-0.975</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.3148</v>
+        <v>-4.8567</v>
       </c>
       <c r="H20" t="n">
-        <v>2.3745</v>
+        <v>-1.1673</v>
       </c>
       <c r="I20" t="n">
-        <v>-5.6893</v>
+        <v>-3.6893</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3333</v>
+        <v>-2.8012</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8358</v>
+        <v>-0.2122</v>
       </c>
       <c r="L20" t="n">
-        <v>-4.1691</v>
+        <v>-2.589</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9815</v>
+        <v>-2.0554</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4613</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5202</v>
+        <v>-1.1003</v>
       </c>
       <c r="P20" t="n">
         <v>1.5441</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5091</v>
+        <v>1.5441</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.2817</v>
+        <v>-0.8622</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2069</v>
+        <v>-1.0126</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0748</v>
+        <v>0.1504</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.5561</v>
+        <v>-0.614</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8999</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. MENDEZ MADERA</t>
+          <t>D. MERKVILADZE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.6974</v>
+        <v>-4.9535</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.2144</v>
+        <v>-4.3618</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.483</v>
+        <v>-0.5917</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.8567</v>
+        <v>-3.3148</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1673</v>
+        <v>2.3745</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.6893</v>
+        <v>-5.6893</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.8012</v>
+        <v>-1.3333</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2122</v>
+        <v>2.8358</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.589</v>
+        <v>-4.1691</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0554</v>
+        <v>-1.9815</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-0.4613</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1003</v>
+        <v>-1.5202</v>
       </c>
       <c r="P21" t="n">
         <v>1.5441</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5441</v>
+        <v>2.5091</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7708</v>
+        <v>-1.6267</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.4132</v>
+        <v>-1.4072</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3576</v>
+        <v>-0.2195</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.614</v>
+        <v>-1.5561</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.614</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.3735</v>
+        <v>-7.0734</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.2923</v>
+        <v>-5.3924</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0812</v>
+        <v>-1.681</v>
       </c>
       <c r="G22" t="n">
         <v>-4.9723</v>
@@ -2170,13 +2170,13 @@
         <v>2.5091</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7523</v>
+        <v>-1.4522</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.3259</v>
+        <v>-1.426</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4264</v>
+        <v>-0.0262</v>
       </c>
       <c r="V22" t="n">
         <v>-1.228</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.438700000000001</v>
+        <v>-8.5983</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.8752</v>
+        <v>-7.2757</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5635</v>
+        <v>-1.3226</v>
       </c>
       <c r="G23" t="n">
         <v>-5.0049</v>
@@ -2248,13 +2248,13 @@
         <v>0.579</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1527</v>
+        <v>-0.3123</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1057</v>
+        <v>-0.5063</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0469</v>
+        <v>0.194</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-39.34440000000001</v>
+        <v>-36.6739</v>
       </c>
       <c r="E24" t="n">
-        <v>-27.4974</v>
+        <v>-27.4973</v>
       </c>
       <c r="F24" t="n">
-        <v>-11.8469</v>
+        <v>-9.176600000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-22.7575</v>
@@ -2326,13 +2326,13 @@
         <v>14.4755</v>
       </c>
       <c r="S24" t="n">
-        <v>-10.4701</v>
+        <v>-7.7997</v>
       </c>
       <c r="T24" t="n">
-        <v>-8.7842</v>
+        <v>-8.7841</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.6857</v>
+        <v>0.9846000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-7.082000000000001</v>
